--- a/output/excel/joint_gap_metrics_joint_gap_c6_u30_k3_s4_seed44.xlsx
+++ b/output/excel/joint_gap_metrics_joint_gap_c6_u30_k3_s4_seed44.xlsx
@@ -544,7 +544,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>26.3646159</v>
+        <v>38.7277972</v>
       </c>
       <c r="M2">
         <v>26620</v>
@@ -567,7 +567,7 @@
         <v>0.06597909062207402</v>
       </c>
       <c r="E3">
-        <v>0.06904649827547699</v>
+        <v>0.069046498275477</v>
       </c>
       <c r="F3">
         <v>0.2138553459112203</v>
@@ -588,7 +588,7 @@
         <v>0.06753620289422643</v>
       </c>
       <c r="L3">
-        <v>4.327167499999998</v>
+        <v>7.173796500000002</v>
       </c>
       <c r="M3">
         <v>8</v>
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6.092811498514909</v>
+        <v>5.398507916972553</v>
       </c>
       <c r="F2">
         <v>305.8245010916258</v>
